--- a/.old/Resultats.xlsx
+++ b/.old/Resultats.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10414"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10102"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kergosien/Desktop/Code Opti Tournées Touristiques + Données/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/pacomerenimel/Code/OptiCheminTouristique/.old/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5207853-0580-F345-8AEF-67BE7959EACF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55DC79DD-6A8E-C945-9E7F-C737E277AA95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2880" yWindow="640" windowWidth="30720" windowHeight="21000" xr2:uid="{EA066B61-4340-A149-91F1-F19407D7865E}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="10000" windowHeight="17400" xr2:uid="{EA066B61-4340-A149-91F1-F19407D7865E}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
   <si>
     <t>Inst1</t>
   </si>
@@ -135,6 +135,33 @@
   </si>
   <si>
     <t>INSTANCES DISPONIBLES</t>
+  </si>
+  <si>
+    <t>Notre solution</t>
+  </si>
+  <si>
+    <t>Poids :</t>
+  </si>
+  <si>
+    <t>popzize 1000</t>
+  </si>
+  <si>
+    <t>elitism 0.05</t>
+  </si>
+  <si>
+    <t>toursize 10</t>
+  </si>
+  <si>
+    <t>mutrate 0.3</t>
+  </si>
+  <si>
+    <t>intensify 0</t>
+  </si>
+  <si>
+    <t>iterations 10000</t>
+  </si>
+  <si>
+    <t>Mo</t>
   </si>
 </sst>
 </file>
@@ -199,7 +226,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office 2013 – 2022">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
     <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
@@ -495,15 +522,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54003879-A489-2749-B9F8-7E0F21DD826C}">
-  <dimension ref="A1:E29"/>
+  <dimension ref="A1:H29"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="14.5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15.1640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14.83203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16" customWidth="1"/>
+    <col min="6" max="6" width="16.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>32</v>
       </c>
@@ -512,7 +541,7 @@
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>27</v>
       </c>
@@ -528,8 +557,17 @@
       <c r="E2" s="1" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F2" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>0</v>
       </c>
@@ -545,8 +583,17 @@
       <c r="E3">
         <v>816</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F3">
+        <v>816</v>
+      </c>
+      <c r="G3">
+        <v>816</v>
+      </c>
+      <c r="H3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>1</v>
       </c>
@@ -562,8 +609,17 @@
       <c r="E4">
         <v>900</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F4">
+        <v>876</v>
+      </c>
+      <c r="G4">
+        <v>852</v>
+      </c>
+      <c r="H4" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>2</v>
       </c>
@@ -579,8 +635,17 @@
       <c r="E5">
         <v>1062</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F5">
+        <v>1002</v>
+      </c>
+      <c r="G5">
+        <v>966</v>
+      </c>
+      <c r="H5" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -596,8 +661,17 @@
       <c r="E6">
         <v>1062</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F6">
+        <v>1062</v>
+      </c>
+      <c r="G6">
+        <v>1062</v>
+      </c>
+      <c r="H6" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>4</v>
       </c>
@@ -613,8 +687,17 @@
       <c r="E7">
         <v>1116</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F7">
+        <v>1044</v>
+      </c>
+      <c r="G7">
+        <v>1014</v>
+      </c>
+      <c r="H7" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>5</v>
       </c>
@@ -630,8 +713,17 @@
       <c r="E8">
         <v>1236</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F8">
+        <v>1200</v>
+      </c>
+      <c r="G8">
+        <v>1092</v>
+      </c>
+      <c r="H8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>6</v>
       </c>
@@ -647,8 +739,14 @@
       <c r="E9">
         <v>1236</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F9">
+        <v>1056</v>
+      </c>
+      <c r="G9">
+        <v>1026</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>7</v>
       </c>
@@ -664,8 +762,14 @@
       <c r="E10">
         <v>1236</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F10">
+        <v>1080</v>
+      </c>
+      <c r="G10">
+        <v>1116</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>8</v>
       </c>
@@ -681,8 +785,14 @@
       <c r="E11">
         <v>1284</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F11">
+        <v>1134</v>
+      </c>
+      <c r="G11">
+        <v>1284</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>9</v>
       </c>
@@ -698,8 +808,14 @@
       <c r="E12">
         <v>1284</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F12">
+        <v>1068</v>
+      </c>
+      <c r="G12">
+        <v>1236</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>10</v>
       </c>
@@ -715,8 +831,11 @@
       <c r="E13">
         <v>1284</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="G13">
+        <v>1164</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>11</v>
       </c>
@@ -732,8 +851,11 @@
       <c r="E14">
         <v>1670</v>
       </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="G14">
+        <v>1390</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>12</v>
       </c>
@@ -749,8 +871,14 @@
       <c r="E15">
         <v>173</v>
       </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F15">
+        <v>160</v>
+      </c>
+      <c r="G15">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>13</v>
       </c>
@@ -766,8 +894,14 @@
       <c r="E16">
         <v>241</v>
       </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F16">
+        <v>241</v>
+      </c>
+      <c r="G16">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>14</v>
       </c>
@@ -783,8 +917,14 @@
       <c r="E17">
         <v>367</v>
       </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F17">
+        <v>367</v>
+      </c>
+      <c r="G17">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>15</v>
       </c>
@@ -800,8 +940,14 @@
       <c r="E18">
         <v>412</v>
       </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F18">
+        <v>399</v>
+      </c>
+      <c r="G18">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>16</v>
       </c>
@@ -817,8 +963,14 @@
       <c r="E19">
         <v>412</v>
       </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F19">
+        <v>393</v>
+      </c>
+      <c r="G19">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>17</v>
       </c>
@@ -834,8 +986,14 @@
       <c r="E20">
         <v>504</v>
       </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F20">
+        <v>504</v>
+      </c>
+      <c r="G20">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>18</v>
       </c>
@@ -851,8 +1009,11 @@
       <c r="E21">
         <v>504</v>
       </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="G21">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>19</v>
       </c>
@@ -868,8 +1029,11 @@
       <c r="E22">
         <v>504</v>
       </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="G22">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>20</v>
       </c>
@@ -885,8 +1049,11 @@
       <c r="E23">
         <v>590</v>
       </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="G23">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>21</v>
       </c>
@@ -902,8 +1069,14 @@
       <c r="E24">
         <v>1114</v>
       </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F24">
+        <v>1088</v>
+      </c>
+      <c r="G24">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>22</v>
       </c>
@@ -919,8 +1092,14 @@
       <c r="E25">
         <v>1164</v>
       </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F25">
+        <v>1158</v>
+      </c>
+      <c r="G25">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>23</v>
       </c>
@@ -936,8 +1115,14 @@
       <c r="E26">
         <v>1234</v>
       </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F26">
+        <v>1100</v>
+      </c>
+      <c r="G26">
+        <v>922</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>24</v>
       </c>
@@ -953,8 +1138,14 @@
       <c r="E27">
         <v>1234</v>
       </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F27">
+        <v>1013</v>
+      </c>
+      <c r="G27">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>25</v>
       </c>
@@ -970,8 +1161,14 @@
       <c r="E28">
         <v>1261</v>
       </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F28">
+        <v>1143</v>
+      </c>
+      <c r="G28">
+        <v>934</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>26</v>
       </c>
@@ -986,6 +1183,12 @@
       </c>
       <c r="E29">
         <v>1306</v>
+      </c>
+      <c r="F29">
+        <v>1154</v>
+      </c>
+      <c r="G29">
+        <v>990</v>
       </c>
     </row>
   </sheetData>

--- a/.old/Resultats.xlsx
+++ b/.old/Resultats.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/pacomerenimel/Code/OptiCheminTouristique/.old/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55DC79DD-6A8E-C945-9E7F-C737E277AA95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89323C76-B072-024D-B51A-F4CCF2100F19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="10000" windowHeight="17400" xr2:uid="{EA066B61-4340-A149-91F1-F19407D7865E}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="50">
   <si>
     <t>Inst1</t>
   </si>
@@ -162,6 +162,30 @@
   </si>
   <si>
     <t>Mo</t>
+  </si>
+  <si>
+    <t>Pop_size 1000</t>
+  </si>
+  <si>
+    <t>Elitism 0.02</t>
+  </si>
+  <si>
+    <t>Tournament 10</t>
+  </si>
+  <si>
+    <t>Mutation rate 0.3</t>
+  </si>
+  <si>
+    <t>Intens_rate 0.01</t>
+  </si>
+  <si>
+    <t>Intens_iter 100</t>
+  </si>
+  <si>
+    <t>Intens_gen_prob 0.01</t>
+  </si>
+  <si>
+    <t>Solution 2</t>
   </si>
 </sst>
 </file>
@@ -522,17 +546,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54003879-A489-2749-B9F8-7E0F21DD826C}">
-  <dimension ref="A1:H29"/>
+  <dimension ref="A1:I38"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="14.5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15.1640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14.83203125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="16" customWidth="1"/>
-    <col min="6" max="6" width="16.1640625" customWidth="1"/>
+    <col min="6" max="7" width="19.6640625" customWidth="1"/>
+    <col min="9" max="9" width="14.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>32</v>
       </c>
@@ -541,7 +566,7 @@
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>27</v>
       </c>
@@ -561,13 +586,16 @@
         <v>33</v>
       </c>
       <c r="G2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>0</v>
       </c>
@@ -586,14 +614,14 @@
       <c r="F3">
         <v>816</v>
       </c>
-      <c r="G3">
+      <c r="H3">
         <v>816</v>
       </c>
-      <c r="H3" t="s">
+      <c r="I3" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>1</v>
       </c>
@@ -612,14 +640,14 @@
       <c r="F4">
         <v>876</v>
       </c>
-      <c r="G4">
+      <c r="H4">
         <v>852</v>
       </c>
-      <c r="H4" t="s">
+      <c r="I4" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>2</v>
       </c>
@@ -639,13 +667,16 @@
         <v>1002</v>
       </c>
       <c r="G5">
+        <v>1026</v>
+      </c>
+      <c r="H5">
         <v>966</v>
       </c>
-      <c r="H5" t="s">
+      <c r="I5" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -664,14 +695,14 @@
       <c r="F6">
         <v>1062</v>
       </c>
-      <c r="G6">
+      <c r="H6">
         <v>1062</v>
       </c>
-      <c r="H6" t="s">
+      <c r="I6" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>4</v>
       </c>
@@ -690,14 +721,14 @@
       <c r="F7">
         <v>1044</v>
       </c>
-      <c r="G7">
+      <c r="H7">
         <v>1014</v>
       </c>
-      <c r="H7" t="s">
+      <c r="I7" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>5</v>
       </c>
@@ -716,14 +747,14 @@
       <c r="F8">
         <v>1200</v>
       </c>
-      <c r="G8">
+      <c r="H8">
         <v>1092</v>
       </c>
-      <c r="H8" t="s">
+      <c r="I8" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>6</v>
       </c>
@@ -742,11 +773,11 @@
       <c r="F9">
         <v>1056</v>
       </c>
-      <c r="G9">
+      <c r="H9">
         <v>1026</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>7</v>
       </c>
@@ -765,11 +796,11 @@
       <c r="F10">
         <v>1080</v>
       </c>
-      <c r="G10">
+      <c r="H10">
         <v>1116</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>8</v>
       </c>
@@ -788,11 +819,11 @@
       <c r="F11">
         <v>1134</v>
       </c>
-      <c r="G11">
+      <c r="H11">
         <v>1284</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>9</v>
       </c>
@@ -811,11 +842,11 @@
       <c r="F12">
         <v>1068</v>
       </c>
-      <c r="G12">
+      <c r="H12">
         <v>1236</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>10</v>
       </c>
@@ -831,11 +862,14 @@
       <c r="E13">
         <v>1284</v>
       </c>
-      <c r="G13">
+      <c r="F13">
+        <v>1230</v>
+      </c>
+      <c r="H13">
         <v>1164</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>11</v>
       </c>
@@ -851,11 +885,14 @@
       <c r="E14">
         <v>1670</v>
       </c>
-      <c r="G14">
+      <c r="F14">
+        <v>1410</v>
+      </c>
+      <c r="H14">
         <v>1390</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>12</v>
       </c>
@@ -874,11 +911,11 @@
       <c r="F15">
         <v>160</v>
       </c>
-      <c r="G15">
+      <c r="H15">
         <v>160</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>13</v>
       </c>
@@ -897,11 +934,11 @@
       <c r="F16">
         <v>241</v>
       </c>
-      <c r="G16">
+      <c r="H16">
         <v>241</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>14</v>
       </c>
@@ -920,11 +957,11 @@
       <c r="F17">
         <v>367</v>
       </c>
-      <c r="G17">
+      <c r="H17">
         <v>367</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>15</v>
       </c>
@@ -943,11 +980,11 @@
       <c r="F18">
         <v>399</v>
       </c>
-      <c r="G18">
+      <c r="H18">
         <v>399</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>16</v>
       </c>
@@ -966,11 +1003,11 @@
       <c r="F19">
         <v>393</v>
       </c>
-      <c r="G19">
+      <c r="H19">
         <v>393</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>17</v>
       </c>
@@ -989,11 +1026,11 @@
       <c r="F20">
         <v>504</v>
       </c>
-      <c r="G20">
+      <c r="H20">
         <v>504</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>18</v>
       </c>
@@ -1009,11 +1046,14 @@
       <c r="E21">
         <v>504</v>
       </c>
-      <c r="G21">
+      <c r="F21">
         <v>504</v>
       </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H21">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>19</v>
       </c>
@@ -1029,11 +1069,14 @@
       <c r="E22">
         <v>504</v>
       </c>
-      <c r="G22">
+      <c r="F22">
         <v>504</v>
       </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H22">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>20</v>
       </c>
@@ -1049,11 +1092,14 @@
       <c r="E23">
         <v>590</v>
       </c>
-      <c r="G23">
+      <c r="F23">
         <v>567</v>
       </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H23">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>21</v>
       </c>
@@ -1072,11 +1118,11 @@
       <c r="F24">
         <v>1088</v>
       </c>
-      <c r="G24">
+      <c r="H24">
         <v>840</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>22</v>
       </c>
@@ -1095,11 +1141,11 @@
       <c r="F25">
         <v>1158</v>
       </c>
-      <c r="G25">
+      <c r="H25">
         <v>857</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>23</v>
       </c>
@@ -1118,11 +1164,11 @@
       <c r="F26">
         <v>1100</v>
       </c>
-      <c r="G26">
+      <c r="H26">
         <v>922</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>24</v>
       </c>
@@ -1141,11 +1187,11 @@
       <c r="F27">
         <v>1013</v>
       </c>
-      <c r="G27">
+      <c r="H27">
         <v>904</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>25</v>
       </c>
@@ -1164,11 +1210,11 @@
       <c r="F28">
         <v>1143</v>
       </c>
-      <c r="G28">
+      <c r="H28">
         <v>934</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>26</v>
       </c>
@@ -1187,8 +1233,48 @@
       <c r="F29">
         <v>1154</v>
       </c>
-      <c r="G29">
+      <c r="H29">
         <v>990</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="F31" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="F32" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="33" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F33" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="34" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F34" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="35" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F35" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="36" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F36" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="37" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F37" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="38" spans="6:6" x14ac:dyDescent="0.2">
+      <c r="F38" t="s">
+        <v>48</v>
       </c>
     </row>
   </sheetData>
